--- a/litreview/coding_exercises.xlsx
+++ b/litreview/coding_exercises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Peter/Library/CloudStorage/Dropbox/papers/2026/wuhan/LitReview-workshop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC3661B-1138-2644-BAC7-C8334962B3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715B9B46-65A1-F347-A265-48AC25507124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="9560" windowWidth="29720" windowHeight="14420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="7300" windowWidth="29720" windowHeight="16520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
     <t xml:space="preserve">Students used microscopes to observe and sketch cells and bacteria.
 They estimated sizes using reference objects and compared different scales.
@@ -101,9 +101,6 @@
     <t>supportedBy</t>
   </si>
   <si>
-    <t>Claim1: Learning irmproves overall</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -137,23 +134,35 @@
     <t>Relate Claim1 to Feature F1</t>
   </si>
   <si>
-    <t>Relate Claim 1 to Feature F1</t>
-  </si>
-  <si>
-    <t>hasResource</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
     <t>Microscope(F1)</t>
+  </si>
+  <si>
+    <t>Claim1: Learning improves overall</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>"Learning improves overall"</t>
+  </si>
+  <si>
+    <t>"Size estimation remains difficult"</t>
+  </si>
+  <si>
+    <t>is_method</t>
+  </si>
+  <si>
+    <t>pre-post test</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -174,6 +183,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -228,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -241,6 +258,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,7 +634,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>18</v>
@@ -699,7 +718,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:D30"/>
+  <dimension ref="A2:D24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="41.5" customWidth="1"/>
@@ -709,39 +728,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
+      <c r="C3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
+      <c r="C4" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -749,102 +769,141 @@
         <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>28</v>
+      <c r="A16" s="5"/>
+      <c r="B16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
+    </row>
+    <row r="20" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -853,36 +912,6 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
